--- a/artfynd/A 5141-2025 artfynd.xlsx
+++ b/artfynd/A 5141-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119697884</v>
+        <v>119697666</v>
       </c>
       <c r="B2" t="n">
-        <v>57471</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,21 +708,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rörsås, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>430980</v>
+        <v>430779</v>
       </c>
       <c r="R2" t="n">
-        <v>6500342</v>
+        <v>6500288</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -790,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119697883</v>
+        <v>119697785</v>
       </c>
       <c r="B3" t="n">
-        <v>57471</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,21 +813,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rörsås, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>431012</v>
+        <v>431191</v>
       </c>
       <c r="R3" t="n">
-        <v>6500336</v>
+        <v>6500493</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,6 +866,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119697947</v>
+        <v>119697663</v>
       </c>
       <c r="B4" t="n">
-        <v>8421</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,34 +900,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rörsås, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430978</v>
+        <v>431031</v>
       </c>
       <c r="R4" t="n">
-        <v>6500370</v>
+        <v>6500422</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,15 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119697663</v>
+        <v>119697802</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,16 +1010,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1051,7 +1034,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1060,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>431031</v>
+        <v>431077</v>
       </c>
       <c r="R5" t="n">
-        <v>6500422</v>
+        <v>6500460</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,12 +1073,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,37 +1109,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119697785</v>
+        <v>119697765</v>
       </c>
       <c r="B6" t="n">
-        <v>80499</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1164,19 +1142,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rörsås, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>431191</v>
+        <v>430936</v>
       </c>
       <c r="R6" t="n">
-        <v>6500493</v>
+        <v>6500374</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,12 +1183,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,7 +1197,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1240,37 +1219,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119697624</v>
+        <v>119697767</v>
       </c>
       <c r="B7" t="n">
-        <v>57801</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1289,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>431016</v>
+        <v>430979</v>
       </c>
       <c r="R7" t="n">
-        <v>6500382</v>
+        <v>6500428</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,12 +1293,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,37 +1329,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119697621</v>
+        <v>119697768</v>
       </c>
       <c r="B8" t="n">
-        <v>57801</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1404,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>431050</v>
+        <v>431160</v>
       </c>
       <c r="R8" t="n">
-        <v>6500359</v>
+        <v>6500396</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1470,15 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119697765</v>
+        <v>119697772</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>430936</v>
+        <v>431133</v>
       </c>
       <c r="R9" t="n">
-        <v>6500374</v>
+        <v>6500048</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,12 +1513,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-13</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,15 +1549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119697772</v>
+        <v>119697621</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,21 +1560,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1634,10 +1593,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>431133</v>
+        <v>431050</v>
       </c>
       <c r="R10" t="n">
-        <v>6500048</v>
+        <v>6500359</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1664,12 +1623,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,37 +1659,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119697666</v>
+        <v>119697624</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1738,16 +1692,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rörsås, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>430779</v>
+        <v>431016</v>
       </c>
       <c r="R11" t="n">
-        <v>6500288</v>
+        <v>6500382</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1774,12 +1733,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,6 +1762,547 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>119697883</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rörsås, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>431012</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6500336</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mariestad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ullervad</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>119697884</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rörsås, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>430980</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6500342</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mariestad</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ullervad</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>119697530</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rörsås, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>430961</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6500412</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mariestad</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ullervad</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>119697834</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rörsås, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>430980</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6500178</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mariestad</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ullervad</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>119697947</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rörsås, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>430978</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6500370</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mariestad</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ullervad</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-05-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 5141-2025 artfynd.xlsx
+++ b/artfynd/A 5141-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697785</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697663</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697666</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697802</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697765</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697767</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,6 +1471,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697768</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1546,6 +1586,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697772</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1656,6 +1701,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697621</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1766,6 +1816,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697624</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1876,6 +1931,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697883</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1986,6 +2046,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697884</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2096,6 +2161,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697530</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2206,6 +2276,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697834</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2307,8 +2382,30 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119697947</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>